--- a/daily_matches/job_matches_2026-03-13.xlsx
+++ b/daily_matches/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G14"/>
+  <dimension ref="A1:G5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Full-Stack AI Engineer (React / Python)</t>
+          <t>Sr. AI Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>17.8</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Hugging Face, Pinecone, Prompt Engineering, TensorFlow, PyTorch, S3, FastAPI</t>
+          <t>AI Engineer, Machine Learning Engineer, RAG, PyTorch, Docker, Kubernetes, Git, Kafka, Hadoop, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,102 +496,102 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bdcc327c07362e</t>
+          <t>https://www.indeed.com/viewjob?jk=580bb2286bd63c0c</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Analytics Engineer, AVS Digital Transformation</t>
+          <t>Applied AI/ML - Senior Associate</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>GE HealthCare</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, Copilot, S3, Glue, Redshift, Dataflow, Git, Redshift, Power BI, Python</t>
+          <t>Generative AI, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, EC2, Glue, Python</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2f0cc5503eaba49f</t>
+          <t>https://www.indeed.com/viewjob?jk=661cecce580f1c89</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Internship, Agentic/Machine Learning Development</t>
+          <t>COE - Data Scientist in QE</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VSP Vision</t>
+          <t>Qualitest</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Mistral, Prompt Engineering, Cortex, TensorFlow, PyTorch, AWS SageMaker, Azure ML, Snowflake</t>
+          <t>Data Scientist, RAG, TensorFlow, XGBoost, CI/CD, Jenkins, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39fd0716d97211ef</t>
+          <t>https://www.indeed.com/viewjob?jk=8612a7749b31e043</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Associate Software Engineer</t>
+          <t>Senior Databricks Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Man Group</t>
+          <t>Concentrix</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, Jenkins, Git, Snowflake, Kafka, PostgreSQL, MongoDB, Dask</t>
+          <t>RAG, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,322 +601,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f28f85e84927f726</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer Senior</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>AmeriHealth Caritas</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D6" t="n">
-        <v>14.4</v>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, Azure ML, MLflow, CI/CD, Databricks, PySpark, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-10</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd2e47e45544341d</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Inventory and POS Revenue Engineer</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>6 points</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Bloomington, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>Docker, Kubernetes, CI/CD, Git, PostgreSQL, MySQL, Python, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7ab4e250f767fcd7</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Intern, Engineering Data Analytics, SmartSense (Boston, MA)</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>SmartSense by Digi</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>Data Scientist, TensorFlow, PyTorch, OpenCV, Git, Snowflake, MySQL, Matplotlib, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=79f9a8056cd4a2b0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>Aspirion</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Columbus, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, MongoDB, Python, SQL, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=96064f52ae049dc5</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Gemini, CI/CD, GitHub Actions, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=70fa9f9ed969637b</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Software Engineer III</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Robert Half</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afc251abc63cd910</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Software Engineer III (Contract Talent)</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>Robert Half</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>San Ramon, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>Generative AI, RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=726e2954e5c38270</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Sr Associate Machine Learning Engineer</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>Workday</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>Boulder, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, Data Scientist, Machine Learning Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=286b968bc855d951</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Senior Data Engineer with AI/ML Focus</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>Tata Consultancy Services (TCS)</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>Sunnyvale, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, S3, Python, SQL, R, Java, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=eeb40d40c729e529</t>
+          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-13.xlsx
+++ b/daily_matches/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G5"/>
+  <dimension ref="A1:G15"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>RHP Properties</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Farmington Hills, MI, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>13.3</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, PyTorch, Docker, Kubernetes, Git, Kafka, Hadoop, Python</t>
+          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=580bb2286bd63c0c</t>
+          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Applied AI/ML - Senior Associate</t>
+          <t>Software Engineer IV - Ruby on Rails</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Paychex, Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Rochester, NY, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>12.2</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Hugging Face, Prompt Engineering, TensorFlow, PyTorch, EC2, Glue, Python</t>
+          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=661cecce580f1c89</t>
+          <t>https://www.indeed.com/viewjob?jk=7a9cc41e94bfd55d</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>COE - Data Scientist in QE</t>
+          <t>Engineer I (Multiple Openings)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Qualitest</t>
+          <t>Samsung Electronics</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, XGBoost, CI/CD, Jenkins, Git, Python, SQL, R</t>
+          <t>RAG, TensorFlow, PyTorch, Hadoop, PostgreSQL, Matplotlib, Python, SQL, R, Bayesian</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8612a7749b31e043</t>
+          <t>https://www.indeed.com/viewjob?jk=8afa99b07bb3eecf</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Databricks Architect</t>
+          <t>Consultant Analytical Engineer Expanse</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Concentrix</t>
+          <t>HCA Healthcare</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,17 +591,367 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, MLflow, CI/CD, Git, Databricks, PySpark, Python, SQL, R, Scala</t>
+          <t>RAG, Redshift, Redshift, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=234f23d56eb992e4</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Advisor Software Engineer (AWS)</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Fannie Mae</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=416fbfefb77d7d3d</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Advisor Software Engineer (AWS)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Fannie Mae</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>AI Engineer, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=811aff7c7e5aac30</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer - Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Guidewire</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>San Mateo, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>AI Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>IN, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, LLaMA, FAISS, FastAPI, Docker, Kubernetes, Python, R</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e04fb47c81a304fe</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior AI Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Allstate Insurance</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, AWS SageMaker, Terraform, Git, Python, R, Scala</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
           <t>2026-03-12</t>
         </is>
       </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4c836fa214ed2bd2</t>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1808d412cb9f0e8a</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Engineer I (Multiple Openings)</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Samsung Electronics</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, FastAPI, Git, PostgreSQL, Matplotlib, Seaborn, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a19684a38c3f90f8</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior Applied ML Scientist</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>SentiLink</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>S3, EC2, Redshift, Git, Redshift, PostgreSQL, Python, SQL, R, Optimization</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=f3f29fb2c620d473</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, AI Coding Tools</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>ByteDance</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>10</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=55767aa3a0381fbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Sr. Software Developer</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AMD</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>San Jose, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>10</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, CI/CD, Hadoop, Python, SQL, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=046da7d204a8ebc1</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Comcast Cybersecurity: Automation Oversight Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Comcast</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>10</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>RAG, Prompt Engineering, Terraform, Git, Tableau, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-12</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e81e8df63edbb1fb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-13.xlsx
+++ b/daily_matches/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>RHP Properties</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Farmington Hills, MI, US USA</t>
+          <t>Bristol, CT, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>13.3</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, Synapse, Data Lake, CI/CD, Git, Snowflake, Databricks, Power BI, Python, SQL</t>
+          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,24 +496,24 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=500303562c165609</t>
+          <t>https://www.indeed.com/viewjob?jk=ab0464aac6bfb39b</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Software Engineer IV - Ruby on Rails</t>
+          <t>Mgr. Software Engineering</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Paychex, Inc.</t>
+          <t>UKG</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Rochester, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,42 +521,42 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Docker, Kubernetes, CI/CD, Git, Kafka, Python, R, Java</t>
+          <t>RAG, Copilot, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-02-11</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7a9cc41e94bfd55d</t>
+          <t>https://www.indeed.com/viewjob?jk=e24063955b9e1ba9</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Engineer I (Multiple Openings)</t>
+          <t>Associate Software Engineer (AI/Machine Learning)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Samsung Electronics</t>
+          <t>Relay</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>12.2</v>
+        <v>11.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>RAG, TensorFlow, PyTorch, Hadoop, PostgreSQL, Matplotlib, Python, SQL, R, Bayesian</t>
+          <t>Data Scientist, RAG, PyTorch, Terraform, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8afa99b07bb3eecf</t>
+          <t>https://www.indeed.com/viewjob?jk=f8f3926268168b5e</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Consultant Analytical Engineer Expanse</t>
+          <t>Sr. Specialist - Database Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>HCA Healthcare</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Nashville, TN, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Redshift, Redshift, Hadoop, Tableau, Power BI, Python, SQL, R, Scala</t>
+          <t>RAG, Copilot, Jenkins, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,357 +601,42 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=234f23d56eb992e4</t>
+          <t>https://www.indeed.com/viewjob?jk=c2ffe0031cb6b91e</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Advisor Software Engineer (AWS)</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Fannie Mae</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Python, R, Java, Scala</t>
+          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=416fbfefb77d7d3d</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>Advisor Software Engineer (AWS)</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Fannie Mae</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D7" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>AI Engineer, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=811aff7c7e5aac30</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer - Cloud Platform</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Guidewire</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>San Mateo, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D8" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=652600a703d693c0</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>AI Engineer</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>IN, US USA</t>
-        </is>
-      </c>
-      <c r="D9" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, LLaMA, FAISS, FastAPI, Docker, Kubernetes, Python, R</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e04fb47c81a304fe</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>Senior AI Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>Allstate Insurance</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D10" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, RAG, Prompt Engineering, AWS SageMaker, Terraform, Git, Python, R, Scala</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1808d412cb9f0e8a</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>Engineer I (Multiple Openings)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>Samsung Electronics</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D11" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>RAG, FastAPI, Git, PostgreSQL, Matplotlib, Seaborn, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a19684a38c3f90f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>Senior Applied ML Scientist</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>SentiLink</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D12" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>S3, EC2, Redshift, Git, Redshift, PostgreSQL, Python, SQL, R, Optimization</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f3f29fb2c620d473</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, AI Coding Tools</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>ByteDance</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D13" t="n">
-        <v>10</v>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>AI Engineer, Machine Learning Engineer, RAG, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=55767aa3a0381fbc</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>Sr. Software Developer</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>AMD</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D14" t="n">
-        <v>10</v>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, CI/CD, Hadoop, Python, SQL, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=046da7d204a8ebc1</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>Comcast Cybersecurity: Automation Oversight Engineer</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>Comcast</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D15" t="n">
-        <v>10</v>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>RAG, Prompt Engineering, Terraform, Git, Tableau, Python, SQL, R, Scala</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e81e8df63edbb1fb</t>
+          <t>https://www.indeed.com/viewjob?jk=b2ab8f72bcb6d8cb</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-13.xlsx
+++ b/daily_matches/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G6"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>IAM Consultant</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Bristol, CT, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>18.9</v>
+        <v>25.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, S3, EC2, Docker, Kubernetes</t>
+          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, CI/CD, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,67 +496,67 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ab0464aac6bfb39b</t>
+          <t>https://www.indeed.com/viewjob?jk=7ec47adf429b46ec</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Mgr. Software Engineering</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>UKG</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>12.2</v>
+        <v>21.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, CI/CD, PostgreSQL, MySQL, MongoDB, Python, SQL, R, Java</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-02-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e24063955b9e1ba9</t>
+          <t>https://www.indeed.com/viewjob?jk=63133dabeeb09c5f</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Associate Software Engineer (AI/Machine Learning)</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Relay</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, PyTorch, Terraform, Git, Python, R, Java, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8f3926268168b5e</t>
+          <t>https://www.indeed.com/viewjob?jk=c18fcc7fd4f16380</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Sr. Specialist - Database Site Reliability Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>AK, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>11.1</v>
+        <v>21.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Jenkins, Terraform, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,42 +601,917 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c2ffe0031cb6b91e</t>
+          <t>https://www.indeed.com/viewjob?jk=28f0e900c27133eb</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>AI Application Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Openkyber</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>21.1</v>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e278edefce8d5cb6</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>AI Integration Engineer (Java + AI)</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D7" t="n">
+        <v>20</v>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, CI/CD, GitHub Actions, Terraform</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D8" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Git, Databricks, Python</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>KONG</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Sacramento, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D9" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Pinecone, Prompt Engineering, Cortex, Snowflake</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee4d205f1d58b062</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Senior Data Engineer</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>KONG</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>US USA</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>16.7</v>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Pinecone, Prompt Engineering, Cortex, Snowflake</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=021ccc88d60d0718</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Karoo Health</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Snowflake, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Karoo Health</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Snowflake, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Senior DevOps Engineer</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Karoo Health</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>15.6</v>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>RAG, S3, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Snowflake, PostgreSQL</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Data Science Intern</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>AARP</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>14.4</v>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>RAG, S3, Redshift, Git, Databricks, Redshift, PySpark, Tableau, Power BI, Python</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0c3f0026666dcfd0</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Aires</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Pittsburgh, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, Docker, CI/CD, Git, SQL, R</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=93069cfd49e3bf96</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Data Lake, Databricks, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Sr. AI Engineer</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>ESP Enterprises</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>TX, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Kubernetes, Python, R</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a72985e869893f92</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Wahl Clipper Corporation</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Sterling, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Data Scientist, CI/CD, Git, Snowflake, PostgreSQL, MySQL, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Network IoT Engineer</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>S3, Glue, Redshift, Git, Databricks, Redshift, Tableau, Power BI, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Snowflake, Python</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=50b96a1eb161feea</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>Data Scientist</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>The Cadmus Group, Inc.</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
           <t>New York, NY, US USA</t>
         </is>
       </c>
-      <c r="D6" t="n">
+      <c r="D21" t="n">
+        <v>13.3</v>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>Data Scientist, RAG, S3, Glue, Data Lake, CI/CD, Git, PySpark, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>2026-03-07</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8c7ca4e70ef5af3a</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D22" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>LangChain, RAG, LLaMA, Copilot, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d42b9fb25c293a0d</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D23" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, CI/CD, Python, R</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e68f60c83bec9e88</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D24" t="n">
+        <v>12.2</v>
+      </c>
+      <c r="E24" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
+        </is>
+      </c>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=60756b0b3883db50</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Cloud AI Application Administrator</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C25" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D25" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G25" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>DevOps/AI Ops Administrator</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C26" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D26" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E26" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G26" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>AI Application Architect</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D27" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>AI Engineer, Generative AI, Copilot, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0bc18e60bdc2ddf4</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>AWS Network Engineer</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>Openkyber</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>AK, US USA</t>
+        </is>
+      </c>
+      <c r="D28" t="n">
+        <v>11.1</v>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>Prompt Engineering, S3, Kinesis, Docker, CI/CD, Jenkins, Git, SQL, R, Java</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>Vaxcyte</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>San Carlos, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D29" t="n">
         <v>10</v>
       </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>Machine Learning Engineer, RAG, TensorFlow, PyTorch, Dask, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>2026-03-12</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b2ab8f72bcb6d8cb</t>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3ee0b8b720e65e91</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer, Machine Learning</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>Anduril</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D30" t="n">
+        <v>10</v>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fdd10eead71e01e</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Sr. Cloud Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Insight</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>Chandler, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D31" t="n">
+        <v>10</v>
+      </c>
+      <c r="E31" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
+        </is>
+      </c>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>2026-03-02</t>
+        </is>
+      </c>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7dca192c0b9630bf</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-13.xlsx
+++ b/daily_matches/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:G17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IAM Consultant</t>
+          <t>Senior AI/ML Engineer - 2349738</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>25.6</v>
+        <v>15.6</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>RAG, S3, Glue, Athena, Redshift, Data Lake, Kinesis, CI/CD, GitHub Actions, Terraform</t>
+          <t>Data Scientist, AWS SageMaker, S3, EC2, Docker, CI/CD, GitHub Actions, Git, NoSQL, Python</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ec47adf429b46ec</t>
+          <t>https://www.indeed.com/viewjob?jk=d97556800e692e01</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Platform Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>AssetMark</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,67 +531,67 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63133dabeeb09c5f</t>
+          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Engineer, Data Analytics Warehousing</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>VNS Health</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.1</v>
+        <v>14.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Data Scientist, Generative AI, S3, Glue, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-11</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c18fcc7fd4f16380</t>
+          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>SAP NS2 Sr. DevOps Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SAP</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.1</v>
+        <v>13.3</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=28f0e900c27133eb</t>
+          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>IT Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.1</v>
+        <v>13.3</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, LLaMA, FAISS, Pinecone, Prompt Engineering, TensorFlow, PyTorch</t>
+          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Kafka, Power BI, Python, R, Java</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e278edefce8d5cb6</t>
+          <t>https://www.indeed.com/viewjob?jk=0a7803539b5e31ca</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>AI Integration Engineer (Java + AI)</t>
+          <t>Senior Software Engineer - 2349742</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>20</v>
+        <v>13.3</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, RAG, BigQuery, Data Lake, Dataflow, Apache Airflow, CI/CD, GitHub Actions, Terraform</t>
+          <t>CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6cd41d8c9a875361</t>
+          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>Senior Salesforce Administrator - Austin, TX ONLY</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Industrial Electric Manufacturing</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>12.2</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer, Generative AI, TensorFlow, PyTorch, MLflow, Kubernetes, CI/CD, Git, Databricks, Python</t>
+          <t>Redshift, CI/CD, Git, Snowflake, Redshift, Tableau, Power BI, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=db4bcb18171633d3</t>
+          <t>https://www.indeed.com/viewjob?jk=a0b0310521ca1215</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Deltek</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Sacramento, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Pinecone, Prompt Engineering, Cortex, Snowflake</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee4d205f1d58b062</t>
+          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist, Generative &amp; Agentic AI Solutions</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>KONG</t>
+          <t>Alvarez &amp; Marsal</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Gemini, Copilot, Pinecone, Prompt Engineering, Cortex, Snowflake</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=021ccc88d60d0718</t>
+          <t>https://www.indeed.com/viewjob?jk=1053b34d9603404d</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Scientist, Generative &amp; Agentic AI Solutions: Senior Consultant</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Alvarez &amp; Marsal</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.6</v>
+        <v>11.1</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Snowflake, PostgreSQL</t>
+          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=858648bbc8cd1e33</t>
+          <t>https://www.indeed.com/viewjob?jk=d17d308f37aaa89e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>AI Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Granum</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Snowflake, PostgreSQL</t>
+          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Cortex, Snowflake, Python, R</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7eda2999554662e7</t>
+          <t>https://www.indeed.com/viewjob?jk=3bb3da405f128d75</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Karoo Health</t>
+          <t>Podium</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.6</v>
+        <v>10</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, S3, Docker, Kubernetes, Apache Airflow, CI/CD, Terraform, Git, Snowflake, PostgreSQL</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=18cf8e2c155436b7</t>
+          <t>https://www.indeed.com/viewjob?jk=aee49142748d3f31</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Science Intern</t>
+          <t>Senior Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>AARP</t>
+          <t>Podium</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Lehi, UT, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>14.4</v>
+        <v>10</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, S3, Redshift, Git, Databricks, Redshift, PySpark, Tableau, Power BI, Python</t>
+          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,32 +916,32 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0c3f0026666dcfd0</t>
+          <t>https://www.indeed.com/viewjob?jk=97520c89ee49c913</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Open Source Contributor</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Aires</t>
+          <t>MERCOR</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, S3, EC2, Docker, CI/CD, Git, SQL, R</t>
+          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=93069cfd49e3bf96</t>
+          <t>https://www.indeed.com/viewjob?jk=cf66698c47fc701e</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI Application Architect</t>
+          <t>AI / LLM Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Openkyber</t>
+          <t>Elite Quests LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>AK, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AI Engineer, RAG, Prompt Engineering, TensorFlow, PyTorch, Azure ML, Data Lake, Databricks, Python, SQL</t>
+          <t>Gemini, Prompt Engineering, S3, Glue, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=53ce4aa52de74c4b</t>
+          <t>https://www.indeed.com/viewjob?jk=facce5ecd2db7266</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Sr. AI Engineer</t>
+          <t>Solutions Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>ESP Enterprises</t>
+          <t>PEAK6</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.3</v>
+        <v>10</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Hugging Face, FAISS, Pinecone, Kubernetes, Python, R</t>
+          <t>RAG, Kinesis, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,497 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a72985e869893f92</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>Wahl Clipper Corporation</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>Sterling, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D18" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>Data Scientist, CI/CD, Git, Snowflake, PostgreSQL, MySQL, Tableau, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3d850942c416047a</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>Network IoT Engineer</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D19" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>S3, Glue, Redshift, Git, Databricks, Redshift, Tableau, Power BI, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1cfa9aa04ecc1a9a</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D20" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, MLflow, Docker, Kubernetes, Snowflake, Python</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=50b96a1eb161feea</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>The Cadmus Group, Inc.</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D21" t="n">
-        <v>13.3</v>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>Data Scientist, RAG, S3, Glue, Data Lake, CI/CD, Git, PySpark, Python, SQL</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>2026-03-07</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8c7ca4e70ef5af3a</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D22" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>LangChain, RAG, LLaMA, Copilot, TensorFlow, PyTorch, CI/CD, Git, Python, R</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d42b9fb25c293a0d</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D23" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, TensorFlow, PyTorch, Docker, CI/CD, Python, R</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e68f60c83bec9e88</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D24" t="n">
-        <v>12.2</v>
-      </c>
-      <c r="E24" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, LangChain, RAG, Hugging Face, TensorFlow, PyTorch, Keras, Python, R</t>
-        </is>
-      </c>
-      <c r="F24" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G24" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=60756b0b3883db50</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Cloud AI Application Administrator</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D25" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E25" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F25" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G25" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4d8830321bc21598</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>DevOps/AI Ops Administrator</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D26" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E26" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, S3, EC2, CI/CD, Terraform, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G26" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a5bae6f3bdfd08c8</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>AI Application Architect</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D27" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E27" t="inlineStr">
-        <is>
-          <t>AI Engineer, Generative AI, Copilot, TensorFlow, PyTorch, Git, Python, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F27" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G27" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0bc18e60bdc2ddf4</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>AWS Network Engineer</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Openkyber</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AK, US USA</t>
-        </is>
-      </c>
-      <c r="D28" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E28" t="inlineStr">
-        <is>
-          <t>Prompt Engineering, S3, Kinesis, Docker, CI/CD, Jenkins, Git, SQL, R, Java</t>
-        </is>
-      </c>
-      <c r="F28" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G28" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=73cda5c026939521</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Vaxcyte</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>San Carlos, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D29" t="n">
-        <v>10</v>
-      </c>
-      <c r="E29" t="inlineStr">
-        <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Terraform, Git, R, Scala, Optimization</t>
-        </is>
-      </c>
-      <c r="F29" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G29" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3ee0b8b720e65e91</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer, Machine Learning</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Anduril</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D30" t="n">
-        <v>10</v>
-      </c>
-      <c r="E30" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Git, Python, R, Java, Scala</t>
-        </is>
-      </c>
-      <c r="F30" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G30" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fdd10eead71e01e</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>Sr. Cloud Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Insight</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>Chandler, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D31" t="n">
-        <v>10</v>
-      </c>
-      <c r="E31" t="inlineStr">
-        <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Jenkins, GitHub Actions, Terraform, Git, R</t>
-        </is>
-      </c>
-      <c r="F31" t="inlineStr">
-        <is>
-          <t>2026-03-02</t>
-        </is>
-      </c>
-      <c r="G31" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=7dca192c0b9630bf</t>
+          <t>https://www.indeed.com/viewjob?jk=880f4b0604d1035f</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-13.xlsx
+++ b/daily_matches/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G17"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior AI/ML Engineer - 2349738</t>
+          <t>GenAI Data Scientist, Commercial, Supply Chain &amp; Trading</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ExxonMobil</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>15.6</v>
+        <v>14.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, AWS SageMaker, S3, EC2, Docker, CI/CD, GitHub Actions, Git, NoSQL, Python</t>
+          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d97556800e692e01</t>
+          <t>https://www.indeed.com/viewjob?jk=6e7ff8b06cafdd44</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Platform Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AssetMark</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chandler, AZ, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>RAG, Copilot, Docker, Kubernetes, AKS, CI/CD, PostgreSQL, Python, SQL, R</t>
+          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,19 +531,19 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ac521d9c6c3e17c</t>
+          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Engineer, Data Analytics Warehousing</t>
+          <t>Pre-Sales Data and AI Architect - Solution Engineering (United States)</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>VNS Health</t>
+          <t>Salesforce</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -552,38 +552,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>14.4</v>
+        <v>13.3</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, S3, Glue, Redshift, CI/CD, Git, Snowflake, Redshift, Python</t>
+          <t>Redshift, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-03-11</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8bea83e1a957a4de</t>
+          <t>https://www.indeed.com/viewjob?jk=0789c6dc6401491c</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>SAP NS2 Sr. DevOps Engineer</t>
+          <t>Engineer/Sr Engineer, IT Software</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>SAP</t>
+          <t>American Airlines</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, S3, EC2, Docker, Kubernetes, CI/CD, Terraform, Git, Python</t>
+          <t>Docker, Kubernetes, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d01cf9363cb3a286</t>
+          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>IT Solutions Architect</t>
+          <t>Agentic AI Engineer - Sea Logistics</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>SCAN Health Plan</t>
+          <t>Kuehne+Nagel</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Long Beach, CA, US USA</t>
+          <t>Detroit, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, GitHub Actions, Terraform, Git, Kafka, Power BI, Python, R, Java</t>
+          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, NoSQL, Python, SQL, R</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,59 +636,59 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a7803539b5e31ca</t>
+          <t>https://www.indeed.com/viewjob?jk=8defb5d075bd5e72</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - 2349742</t>
+          <t>Software Engineer II</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Chewy</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>13.3</v>
+        <v>12.2</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CI/CD, GitHub Actions, Terraform, Git, Snowflake, Databricks, Tableau, Power BI, SQL, R</t>
+          <t>Data Scientist, RAG, CI/CD, Jenkins, Terraform, NoSQL, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-03-12</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=47a5ec5630dae169</t>
+          <t>https://www.indeed.com/viewjob?jk=ed675b1b00caf091</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Salesforce Administrator - Austin, TX ONLY</t>
+          <t>Intern, Data Science, AI and Business Analytics</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Industrial Electric Manufacturing</t>
+          <t>Coherent Corp.</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Santa Clara, CA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Redshift, CI/CD, Git, Snowflake, Redshift, Tableau, Power BI, SQL, R, Scala</t>
+          <t>Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, Tableau, Matplotlib, Python, SQL, R</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0b0310521ca1215</t>
+          <t>https://www.indeed.com/viewjob?jk=e66d0681c72af81c</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate - Software Engineer - AI &amp; Cloud Platforms</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Deltek</t>
+          <t>New York Life</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,42 +731,42 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, GitHub Actions, Git, PostgreSQL, Python, SQL, R</t>
+          <t>Data Scientist, LangChain, RAG, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-03-13</t>
+          <t>2026-02-25</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f1e28a487903057</t>
+          <t>https://www.indeed.com/viewjob?jk=ea10728a94bf86ea</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative &amp; Agentic AI Solutions</t>
+          <t>AL/ML Technical Architect</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
+          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, PySpark, Python, R, Scala</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1053b34d9603404d</t>
+          <t>https://www.indeed.com/viewjob?jk=575f36ba7670277a</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative &amp; Agentic AI Solutions: Senior Consultant</t>
+          <t>Technical Architect</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Alvarez &amp; Marsal</t>
+          <t>Tata Consultancy Services (TCS)</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Manchester, CT, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>11.1</v>
+        <v>10</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Data Scientist, Generative AI, LangChain, RAG, PyTorch, EC2, FastAPI, Python, SQL, R</t>
+          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,24 +811,24 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d17d308f37aaa89e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad96610a84402795</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Granum</t>
+          <t>Inpro Corporation</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Muskego, WI, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, LLaMA, Pinecone, Cortex, Snowflake, Python, R</t>
+          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,24 +846,24 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bb3da405f128d75</t>
+          <t>https://www.indeed.com/viewjob?jk=f5ffc03754d12def</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Transportation Data Scientist (Assistant Research Engineer)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Podium</t>
+          <t>University of Maryland University College</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>College Park, MD, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>Data Scientist, RAG, Git, Hadoop, Python, SQL, R, Java, Scala</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=aee49142748d3f31</t>
+          <t>https://www.indeed.com/viewjob?jk=7e0bc7c5e3622123</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Site Reliability Engineer</t>
+          <t>Senior Data Analyst</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Podium</t>
+          <t>Nira Medical</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Lehi, UT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Docker, Kubernetes, CI/CD, Terraform, Git, Python, R, Scala</t>
+          <t>RAG, Cortex, Athena, Snowflake, Tableau, Power BI, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=97520c89ee49c913</t>
+          <t>https://www.indeed.com/viewjob?jk=cc36b42f17068ffe</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Open Source Contributor</t>
+          <t>AI Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>MERCOR</t>
+          <t>US Bolt Manufacturing</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RAG, Docker, CI/CD, GitHub Actions, Git, Python, R, Java, Scala</t>
+          <t>TensorFlow, PyTorch, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,24 +951,24 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf66698c47fc701e</t>
+          <t>https://www.indeed.com/viewjob?jk=afa354da2775c073</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AI / LLM Engineer</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Elite Quests LLC</t>
+          <t>Baylor Miraca Genetics Laboratories LLC</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>Gemini, Prompt Engineering, S3, Glue, Python, R, Java, Scala, Optimization</t>
+          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,42 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=facce5ecd2db7266</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>Solutions Engineer</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>PEAK6</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D17" t="n">
-        <v>10</v>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>RAG, Kinesis, Docker, Kubernetes, Git, Kafka, Python, R, Java</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>2026-03-13</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=880f4b0604d1035f</t>
+          <t>https://www.indeed.com/viewjob?jk=22b9fc78e83c8b0c</t>
         </is>
       </c>
     </row>

--- a/daily_matches/job_matches_2026-03-13.xlsx
+++ b/daily_matches/job_matches_2026-03-13.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G16"/>
+  <dimension ref="A1:G19"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,25 +468,25 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>GenAI Data Scientist, Commercial, Supply Chain &amp; Trading</t>
+          <t>Associate Data Scientist</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>ExxonMobil</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Nashville, TN, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>14.4</v>
+        <v>18.9</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Data Scientist, Machine Learning Engineer, Generative AI, LangChain, RAG, Copilot, Prompt Engineering, TensorFlow, PyTorch, Git</t>
+          <t>Data Scientist, Generative AI, RAG, Gemini, BigQuery, Dataflow, CI/CD, Terraform, Git, Databricks</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
@@ -496,32 +496,32 @@
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6e7ff8b06cafdd44</t>
+          <t>https://www.indeed.com/viewjob?jk=52f111d99c03d0f9</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Python + AI + AWS Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>VeeRteq Solutions Inc.</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chandler, AZ, US USA</t>
+          <t>Houston, IL, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>13.3</v>
+        <v>17.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Generative AI, Synapse, CI/CD, Jenkins, GitHub Actions, Terraform, Git, Databricks, Python, R</t>
+          <t>Generative AI, RAG, Hugging Face, TensorFlow, PyTorch, S3, EC2, FastAPI, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
@@ -531,32 +531,32 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61994c624b012a49</t>
+          <t>https://www.indeed.com/viewjob?jk=f65c08b46236d9db</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Pre-Sales Data and AI Architect - Solution Engineering (United States)</t>
+          <t>Analytics, Full-Stack Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Salesforce</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Long Beach, CA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Redshift, BigQuery, Data Lake, Snowflake, Databricks, BigQuery, Redshift, Tableau, Power BI, Python</t>
+          <t>AI Engineer, Data Scientist, Generative AI, RAG, Cortex, CI/CD, Snowflake, Databricks, PySpark, Power BI</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0789c6dc6401491c</t>
+          <t>https://www.indeed.com/viewjob?jk=381b905fbb17a824</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Engineer/Sr Engineer, IT Software</t>
+          <t>Senior ML Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>American Airlines</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>13.3</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Docker, Kubernetes, GitHub Actions, Terraform, Git, Kafka, PostgreSQL, MongoDB, Python, SQL</t>
+          <t>Data Scientist, TensorFlow, XGBoost, S3, Athena, Data Lake, FastAPI, Kubernetes, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4273480495ae1f7a</t>
+          <t>https://www.indeed.com/viewjob?jk=c2662d7bd818f7f6</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Agentic AI Engineer - Sea Logistics</t>
+          <t>Cloud Migration Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kuehne+Nagel</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AI Engineer, LangChain, RAG, Prompt Engineering, Docker, Kubernetes, NoSQL, Python, SQL, R</t>
+          <t>Generative AI, RAG, Gemini, S3, EC2, CI/CD, Jenkins, GitHub Actions, Terraform, Git</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8defb5d075bd5e72</t>
+          <t>https://www.indeed.com/viewjob?jk=74a47a5fd7f767fe</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Software Engineer II</t>
+          <t>Data Scientist, Innovation Lab - Remote</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Chewy</t>
+          <t>Experian</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>12.2</v>
+        <v>15.6</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, CI/CD, Jenkins, Terraform, NoSQL, Python, SQL, R, Java</t>
+          <t>Data Scientist, Generative AI, RAG, TensorFlow, PyTorch, Keras, PySpark, Hadoop, MongoDB, Cassandra</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-03-12</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed675b1b00caf091</t>
+          <t>https://www.indeed.com/viewjob?jk=16dbecd15c078f47</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Intern, Data Science, AI and Business Analytics</t>
+          <t>Data Engineer - Senior</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Coherent Corp.</t>
+          <t>Cummins</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Santa Clara, CA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>12.2</v>
+        <v>13.3</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, LLaMA, Gemini, Prompt Engineering, Tableau, Matplotlib, Python, SQL, R</t>
+          <t>RAG, Data Lake, CI/CD, Git, Databricks, Kafka, Python, SQL, R, Java</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,67 +706,67 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e66d0681c72af81c</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bee0d4a42c16ed</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Associate - Software Engineer - AI &amp; Cloud Platforms</t>
+          <t>Data Scientist II / Data Solutions Developer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>New York Life</t>
+          <t>HDR</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>11.1</v>
+        <v>12.2</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data Scientist, LangChain, RAG, CI/CD, Terraform, Git, Python, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Tableau, Power BI, Matplotlib, Seaborn, Python, SQL, R, Scala</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-02-25</t>
+          <t>2026-03-13</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea10728a94bf86ea</t>
+          <t>https://www.indeed.com/viewjob?jk=83d45826a3278dad</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>AL/ML Technical Architect</t>
+          <t>Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Ibotta</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, TensorFlow, PyTorch, CI/CD, PySpark, Python, R, Scala</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, XGBoost, Data Lake, CI/CD, Git, Python, SQL, R</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,32 +776,32 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=575f36ba7670277a</t>
+          <t>https://www.indeed.com/viewjob?jk=1ebfb4618297b7d4</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Technical Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Tata Consultancy Services (TCS)</t>
+          <t>Redwood Logistics</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Manchester, CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Generative AI, RAG, Prompt Engineering, TensorFlow, PyTorch, Python, R, Scala, Optimization</t>
+          <t>Data Scientist, Machine Learning Engineer, RAG, Redshift, Snowflake, Databricks, Redshift, Python, SQL, R</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
@@ -811,32 +811,32 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad96610a84402795</t>
+          <t>https://www.indeed.com/viewjob?jk=0c4e7ef8e71a09f6</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Engineer III - Full Stack Generative AI/LLM</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Inpro Corporation</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Muskego, WI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Jenkins, GitHub Actions, Git, Python, SQL, R, Scala</t>
+          <t>Generative AI, RAG, Hugging Face, Prompt Engineering, Jenkins, Git, Python, R, Java, Scala</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f5ffc03754d12def</t>
+          <t>https://www.indeed.com/viewjob?jk=9d6e79dde744096a</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Transportation Data Scientist (Assistant Research Engineer)</t>
+          <t>AI Agent Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>University of Maryland University College</t>
+          <t>Momentive Software</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>College Park, MD, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Data Scientist, RAG, Git, Hadoop, Python, SQL, R, Java, Scala</t>
+          <t>Data Scientist, RAG, Athena, Data Lake, Kubernetes, CI/CD, Terraform, Python, R, Java</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,32 +881,32 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7e0bc7c5e3622123</t>
+          <t>https://www.indeed.com/viewjob?jk=f59c40422f4d27b8</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Data Architect - T7</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Nira Medical</t>
+          <t>NielsenIQ</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>10</v>
+        <v>12.2</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RAG, Cortex, Athena, Snowflake, Tableau, Power BI, Python, SQL, R</t>
+          <t>Data Scientist, Data Lake, Docker, Kubernetes, Snowflake, Databricks, PySpark, Python, SQL, R</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc36b42f17068ffe</t>
+          <t>https://www.indeed.com/viewjob?jk=2f81821b15c92cc4</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AI Architect</t>
+          <t>AI &amp; Cloud Architect</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>US Bolt Manufacturing</t>
+          <t>SCAN Health Plan</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Lakewood, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>TensorFlow, PyTorch, Data Lake, Git, Python, SQL, R, Scala, Optimization</t>
+          <t>AI Engineer, RAG, Azure ML, CI/CD, Snowflake, Databricks, R, Scala, Optimization</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,19 +951,19 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afa354da2775c073</t>
+          <t>https://www.indeed.com/viewjob?jk=9c94e92bdedec4b3</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Baylor Miraca Genetics Laboratories LLC</t>
+          <t>GitHub</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>RAG, CI/CD, Git, PostgreSQL, MySQL, SQL, R, Scala, Optimization</t>
+          <t>RAG, Copilot, CI/CD, Git, Python, R, Java, Scala, Optimization</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,112 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22b9fc78e83c8b0c</t>
+          <t>https://www.indeed.com/viewjob?jk=8fa85517e4057876</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Cloud Engineer – Managed IT Services (5117)</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>SMX</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Columbia, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>10</v>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, Terraform, Git, Python, R, Scala, Optimization</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c90c9f879d0dae92</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>Klaviyo</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Boston, MA, US USA</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>10</v>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>Kubernetes, CI/CD, Git, MySQL, NoSQL, Python, SQL, R, A/B Testing</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d1ae2928de2e5dbc</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Engineer, Senior Systems</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>Austin Community College</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>10</v>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>RAG, Docker, Kubernetes, AKS, Git, Python, SQL, R, Scala</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>2026-03-13</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6c689565aa612dfb</t>
         </is>
       </c>
     </row>
